--- a/productos/avance/avance_censos_historicos.xlsx
+++ b/productos/avance/avance_censos_historicos.xlsx
@@ -157,7 +157,7 @@
     <t>Parroquia × sexo × edad (pág. 386, PDF 419) y subdelegación/distrito × sexo × edad desde los bloques provinciales (p. ej. Coquimbo, PDF 302).</t>
   </si>
   <si>
-    <t>Departamento × sexo × edad en 6 tramos (pág. 352) y provincia × sexo × edad (pág. 360) desde la propia publicación; valida 1952 C5 y C6. Departamento (total) desde su sinóptico, validado con el de 1875; provincia × área (1952 C9). Escaneo malo: cifras dudosas fijadas con sumas por fila y por provincia. Errata: Caupolicán 16–25 hombres.</t>
+    <t>Departamento × sexo × edad en 6 tramos (pág. 352) y provincia × sexo × edad (pág. 360) desde la propia publicación; valida 1952 C5 y C6. Departamento (total) desde su sinóptico, validado con el de 1875; provincia × área (1952 C9). Escaneo malo: cifras dudosas fijadas con sumas por fila y por provincia y revisadas con la copia de Memoria Chilena (4 corregidas en Itata y Linares). Erratas: Caupolicán 16–25 hombres y Quinchao hasta 7 hombres.</t>
   </si>
   <si>
     <t>pub_1875</t>
@@ -6433,7 +6433,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>1865</v>
       </c>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="U9" s="7">
         <f>SUMIFS(Cifras!$J$2:$J$399,Cifras!$A$2:$A$399,$A9)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V9" s="13" t="s">
         <v>40</v>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="U21" s="17">
         <f>SUM(U5:U20)</f>
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.25">
@@ -8681,7 +8681,7 @@
         <v>634</v>
       </c>
       <c r="J31" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -50013,7 +50013,7 @@
       </c>
       <c r="M5" s="22">
         <f>SUMIFS(Cifras!$J$2:$J$399,Cifras!$B$2:$B$399,B5,Cifras!$C$2:$C$399,C5)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" s="20" t="s">
         <v>1679</v>
@@ -51827,7 +51827,7 @@
       </c>
       <c r="M45" s="23">
         <f>SUM(M2:M44)</f>
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
